--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18481,7 +18481,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29803,7 +29803,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30607,7 +30607,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32762,7 +32762,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33164,7 +33164,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35866,7 +35866,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36268,7 +36268,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37217,7 +37217,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38825,7 +38825,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39774,7 +39774,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40578,7 +40578,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41527,7 +41527,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -41929,7 +41929,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42331,7 +42331,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43682,7 +43682,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44084,7 +44084,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45033,7 +45033,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45837,7 +45837,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46239,7 +46239,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46786,7 +46786,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47188,7 +47188,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47590,7 +47590,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47992,7 +47992,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48941,7 +48941,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49343,7 +49343,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49745,7 +49745,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50694,7 +50694,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51096,7 +51096,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51498,7 +51498,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51900,7 +51900,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52447,7 +52447,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52849,7 +52849,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53653,7 +53653,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55004,7 +55004,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55406,7 +55406,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55808,7 +55808,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5024,6 +5129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6777,6 +6887,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8530,6 +8645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10685,6 +10805,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12438,6 +12563,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14191,6 +14321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16346,6 +16481,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18099,6 +18239,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19852,6 +19997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22007,6 +22157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23760,6 +23915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25915,6 +26075,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27668,6 +27833,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29421,6 +29591,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31576,6 +31751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33329,6 +33509,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35082,6 +35267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36835,6 +37025,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38990,6 +39185,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40743,6 +40943,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42898,6 +43103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44651,6 +44861,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46404,6 +46619,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48559,6 +48779,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50312,6 +50537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52065,6 +52295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54218,6 +54453,11 @@
       <c r="S281" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19028,7 +19028,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19832,7 +19832,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22544,7 +22544,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23348,7 +23348,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24302,7 +24302,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24704,7 +24704,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25910,7 +25910,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26462,7 +26462,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28220,7 +28220,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28622,7 +28622,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29024,7 +29024,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29978,7 +29978,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30380,7 +30380,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30782,7 +30782,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31184,7 +31184,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31586,7 +31586,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32540,7 +32540,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32942,7 +32942,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33344,7 +33344,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34298,7 +34298,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34700,7 +34700,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -35102,7 +35102,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35654,7 +35654,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36056,7 +36056,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36458,7 +36458,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36860,7 +36860,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37412,7 +37412,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37814,7 +37814,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38216,7 +38216,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38618,7 +38618,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39572,7 +39572,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39974,7 +39974,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40376,7 +40376,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40778,7 +40778,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41330,7 +41330,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41732,7 +41732,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -42134,7 +42134,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42536,7 +42536,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42938,7 +42938,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43490,7 +43490,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43892,7 +43892,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44294,7 +44294,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44696,7 +44696,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45248,7 +45248,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -46052,7 +46052,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46454,7 +46454,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47006,7 +47006,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47408,7 +47408,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47810,7 +47810,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48212,7 +48212,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48614,7 +48614,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49166,7 +49166,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49568,7 +49568,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49970,7 +49970,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50372,7 +50372,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50924,7 +50924,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51326,7 +51326,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51728,7 +51728,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -52130,7 +52130,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52682,7 +52682,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -53084,7 +53084,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53486,7 +53486,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53888,7 +53888,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54290,7 +54290,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54842,7 +54842,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55244,7 +55244,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55646,7 +55646,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -56048,7 +56048,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1518,11 +1443,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,22 +1455,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1668,11 +1578,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1818,11 +1713,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1968,11 +1848,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,22 +1860,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2118,11 +1983,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1995,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2268,11 +2118,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,22 +2130,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2418,11 +2253,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,22 +2265,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2568,11 +2388,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,22 +2400,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2718,11 +2523,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,22 +2535,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2868,11 +2658,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,22 +2670,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3018,11 +2793,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,22 +2805,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3168,11 +2928,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,22 +2940,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3318,11 +3063,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3075,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3468,11 +3198,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,22 +3210,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3618,11 +3333,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,22 +3345,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3768,11 +3468,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3480,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -5124,11 +4809,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5141,22 +4821,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -6882,11 +6552,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6899,22 +6564,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -8640,11 +8295,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8657,22 +8307,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -10800,11 +10440,6 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10817,22 +10452,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -12558,11 +12183,6 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12575,22 +12195,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -14316,11 +13926,6 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14333,22 +13938,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -16476,11 +16071,6 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16493,22 +16083,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -18234,11 +17814,6 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18251,22 +17826,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -19992,11 +19557,6 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20009,22 +19569,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -22152,11 +21702,6 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22169,22 +21714,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -23910,11 +23445,6 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23927,22 +23457,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -26070,11 +25590,6 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26087,22 +25602,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -27828,11 +27333,6 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27845,22 +27345,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -29586,11 +29076,6 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29603,22 +29088,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -31746,11 +31221,6 @@
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31763,22 +31233,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -33504,11 +32964,6 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33521,22 +32976,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -35262,11 +34707,6 @@
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35279,22 +34719,12 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -37020,11 +36450,6 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37037,22 +36462,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -39180,11 +38595,6 @@
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39197,22 +38607,12 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -40938,11 +40338,6 @@
       <c r="R212" t="n">
         <v>0</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40955,22 +40350,12 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
-      </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -43098,11 +42483,6 @@
       <c r="R223" t="n">
         <v>0</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43115,22 +42495,12 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
-      </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -44856,11 +44226,6 @@
       <c r="R232" t="n">
         <v>0</v>
       </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44873,22 +44238,12 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
         <v>0</v>
-      </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
@@ -46614,11 +45969,6 @@
       <c r="R241" t="n">
         <v>0</v>
       </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46631,22 +45981,12 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
         <v>0</v>
-      </c>
-      <c r="AU241" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
@@ -48774,11 +48114,6 @@
       <c r="R252" t="n">
         <v>0</v>
       </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48791,22 +48126,12 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
-      </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
@@ -50532,11 +49857,6 @@
       <c r="R261" t="n">
         <v>0</v>
       </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50549,22 +49869,12 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
         <v>0</v>
-      </c>
-      <c r="AU261" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
@@ -52290,11 +51600,6 @@
       <c r="R270" t="n">
         <v>0</v>
       </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52307,22 +51612,12 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
         <v>0</v>
-      </c>
-      <c r="AU270" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
@@ -54450,11 +53745,6 @@
       <c r="R281" t="n">
         <v>0</v>
       </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54467,22 +53757,12 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR281" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr"/>
       <c r="AT281" t="n">
         <v>0</v>
-      </c>
-      <c r="AU281" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,12 +1235,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,12 +1385,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1443,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,12 +1535,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1578,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,12 +1685,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1713,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1848,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,12 +1985,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1983,6 +2118,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,12 +2135,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2118,6 +2268,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,12 +2285,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2253,6 +2418,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,12 +2435,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2388,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,12 +2585,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2523,6 +2718,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,12 +2735,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2658,6 +2868,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,12 +2885,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2793,6 +3018,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,12 +3035,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2928,6 +3168,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,12 +3185,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3063,6 +3318,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,12 +3335,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3198,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,12 +3485,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3333,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,12 +3635,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3468,6 +3768,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,12 +3785,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4053,6 +4368,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4065,12 +4385,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4788,6 +5118,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4800,12 +5135,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5523,6 +5868,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5535,12 +5885,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6408,6 +6768,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6420,12 +6785,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7143,6 +7518,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7155,12 +7535,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7878,6 +8268,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7890,12 +8285,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8763,6 +9168,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8775,12 +9185,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9498,6 +9918,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9510,12 +9935,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10233,6 +10668,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10245,12 +10685,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11118,6 +11568,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11130,12 +11585,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11853,6 +12318,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11865,12 +12335,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12738,6 +13218,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12750,12 +13235,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13473,6 +13968,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13485,12 +13985,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14208,6 +14718,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14220,12 +14735,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15093,6 +15618,11 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15105,12 +15635,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15828,6 +16368,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15840,12 +16385,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16563,6 +17118,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16575,12 +17135,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17298,6 +17868,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17310,12 +17885,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18183,6 +18768,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18195,12 +18785,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -18918,6 +19518,11 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18930,12 +19535,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19803,6 +20418,11 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19815,12 +20435,22 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20538,6 +21168,11 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20550,12 +21185,22 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21273,6 +21918,11 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21285,12 +21935,22 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22158,6 +22818,11 @@
       <c r="R149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22170,12 +22835,22 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -22893,6 +23568,11 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22905,12 +23585,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -23628,6 +24318,11 @@
       <c r="R159" t="n">
         <v>0</v>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23640,12 +24335,22 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -24513,6 +25218,11 @@
       <c r="R165" t="n">
         <v>0</v>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24525,12 +25235,22 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
